--- a/services/integrator/internal/document/testdata/kartu-stok-q1-2026.golden.xlsx
+++ b/services/integrator/internal/document/testdata/kartu-stok-q1-2026.golden.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">PT Stok Uji</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gula Aren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayu Manis</t>
   </si>
   <si>
     <t xml:space="preserve">Kopi Arabika</t>
@@ -342,42 +345,42 @@
         <v>12</v>
       </c>
       <c r="C10" s="7">
-        <v>7.625</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7">
-        <v>6.375</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="7">
-        <v>4.334</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7">
         <v>0</v>
       </c>
       <c r="G10" s="7">
-        <v>9.666</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="7">
-        <v>0</v>
+        <v>7.625</v>
       </c>
       <c r="D11" s="7">
-        <v>7</v>
+        <v>6.375</v>
       </c>
       <c r="E11" s="7">
-        <v>7</v>
+        <v>4.334</v>
       </c>
       <c r="F11" s="7">
         <v>0</v>
       </c>
       <c r="G11" s="7">
-        <v>0</v>
+        <v>9.666</v>
       </c>
     </row>
     <row r="12">
@@ -391,16 +394,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="7">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="7">
         <v>0</v>
       </c>
       <c r="G12" s="7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -414,7 +417,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="7">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="E13" s="7">
         <v>0</v>
@@ -423,7 +426,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="7">
-        <v>1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -431,68 +434,68 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C14" s="7">
         <v>0</v>
       </c>
       <c r="D14" s="7">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7">
         <v>0</v>
       </c>
       <c r="G14" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
       <c r="C15" s="7">
         <v>0</v>
       </c>
       <c r="D15" s="7">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="E15" s="7">
-        <v>5.5</v>
+        <v>0.3</v>
       </c>
       <c r="F15" s="7">
         <v>0</v>
       </c>
       <c r="G15" s="7">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
       <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.3</v>
+        <v>5.5</v>
       </c>
       <c r="F16" s="7">
         <v>0</v>
       </c>
       <c r="G16" s="7">
-        <v>0.2</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="17">
@@ -500,22 +503,22 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C17" s="7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="7">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="F17" s="7">
         <v>0</v>
       </c>
       <c r="G17" s="7">
-        <v>4.6499999999999995</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18">
@@ -523,70 +526,93 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C18" s="7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="D18" s="7">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="E18" s="7">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="F18" s="7">
         <v>0</v>
       </c>
       <c r="G18" s="7">
-        <v>3</v>
+        <v>4.6499999999999995</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
       <c r="C19" s="7">
         <v>0</v>
       </c>
       <c r="D19" s="7">
+        <v>4</v>
+      </c>
+      <c r="E19" s="7">
         <v>1</v>
       </c>
-      <c r="E19" s="7">
-        <v>0</v>
-      </c>
       <c r="F19" s="7">
         <v>0</v>
       </c>
       <c r="G19" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="7">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="9">
+      <c r="E20" s="7">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="9">
         <v>34.375</v>
       </c>
-      <c r="D20" s="9">
-        <v>180.675</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="D21" s="9">
+        <v>181.175</v>
+      </c>
+      <c r="E21" s="9">
         <v>82.634</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F21" s="9">
         <v>7.375</v>
       </c>
-      <c r="G20" s="9">
-        <v>132.416</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>28</v>
+      <c r="G21" s="9">
+        <v>132.916</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
